--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/37.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/37.xlsx
@@ -426,13 +426,13 @@
         <v>-22.17270584149289</v>
       </c>
       <c r="E2">
-        <v>-9.283339545812149</v>
+        <v>-6.752497160801381</v>
       </c>
       <c r="F2">
-        <v>4.030148918197966</v>
+        <v>2.952910126370988</v>
       </c>
       <c r="G2">
-        <v>-18.65294325867226</v>
+        <v>-16.19367929022454</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.39494618229056</v>
       </c>
       <c r="E3">
-        <v>-10.1481295142906</v>
+        <v>-7.261531353617666</v>
       </c>
       <c r="F3">
-        <v>4.194831671344119</v>
+        <v>3.014171209277622</v>
       </c>
       <c r="G3">
-        <v>-17.0061717251695</v>
+        <v>-15.09500356006323</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.32246609455162</v>
       </c>
       <c r="E4">
-        <v>-11.19578537740125</v>
+        <v>-7.301717826396708</v>
       </c>
       <c r="F4">
-        <v>4.094349048649733</v>
+        <v>2.623685442537158</v>
       </c>
       <c r="G4">
-        <v>-17.10746208844322</v>
+        <v>-15.11169405023422</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.03643362825997</v>
       </c>
       <c r="E5">
-        <v>-11.09319275125533</v>
+        <v>-7.713899131117992</v>
       </c>
       <c r="F5">
-        <v>4.574555288787412</v>
+        <v>3.328886209684016</v>
       </c>
       <c r="G5">
-        <v>-16.18374279631077</v>
+        <v>-14.88970504839644</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.57512065656632</v>
       </c>
       <c r="E6">
-        <v>-11.02164953297384</v>
+        <v>-8.244189459494748</v>
       </c>
       <c r="F6">
-        <v>4.068161041577629</v>
+        <v>3.440129324940767</v>
       </c>
       <c r="G6">
-        <v>-15.14402551125056</v>
+        <v>-14.26012268487718</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.998032237241</v>
       </c>
       <c r="E7">
-        <v>-12.07774056828521</v>
+        <v>-9.60790470442485</v>
       </c>
       <c r="F7">
-        <v>4.677733419010507</v>
+        <v>2.992083620849376</v>
       </c>
       <c r="G7">
-        <v>-15.95577780010394</v>
+        <v>-14.19730947538729</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.37152185386414</v>
       </c>
       <c r="E8">
-        <v>-13.22005642391135</v>
+        <v>-9.420727776437477</v>
       </c>
       <c r="F8">
-        <v>4.449599379544718</v>
+        <v>3.495316818050076</v>
       </c>
       <c r="G8">
-        <v>-15.8768197460626</v>
+        <v>-13.80361832865347</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.74691493563289</v>
       </c>
       <c r="E9">
-        <v>-13.26028442880364</v>
+        <v>-10.3733332451681</v>
       </c>
       <c r="F9">
-        <v>4.706923429550356</v>
+        <v>3.609616609023158</v>
       </c>
       <c r="G9">
-        <v>-14.09367466347075</v>
+        <v>-13.54100614097798</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.18543623132903</v>
       </c>
       <c r="E10">
-        <v>-13.37021577936053</v>
+        <v>-10.77524781149441</v>
       </c>
       <c r="F10">
-        <v>4.790467595592298</v>
+        <v>3.907184404191602</v>
       </c>
       <c r="G10">
-        <v>-13.6394468765305</v>
+        <v>-13.45182702186244</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.711129455182244</v>
       </c>
       <c r="E11">
-        <v>-14.45498473886985</v>
+        <v>-11.99623794924678</v>
       </c>
       <c r="F11">
-        <v>4.739806301971885</v>
+        <v>4.010278040939611</v>
       </c>
       <c r="G11">
-        <v>-12.96225105853081</v>
+        <v>-12.55791721147132</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.364713360943435</v>
       </c>
       <c r="E12">
-        <v>-14.46310426700989</v>
+        <v>-12.14059111526384</v>
       </c>
       <c r="F12">
-        <v>5.648704270201947</v>
+        <v>4.225332159115196</v>
       </c>
       <c r="G12">
-        <v>-13.70861072223827</v>
+        <v>-11.5499035033533</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.141905535018094</v>
       </c>
       <c r="E13">
-        <v>-17.19447615441735</v>
+        <v>-12.14096075107175</v>
       </c>
       <c r="F13">
-        <v>5.35138995545876</v>
+        <v>4.339395037011077</v>
       </c>
       <c r="G13">
-        <v>-12.03219026778654</v>
+        <v>-11.33548305008516</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.065265785505913</v>
       </c>
       <c r="E14">
-        <v>-16.2746852083642</v>
+        <v>-13.84434223099163</v>
       </c>
       <c r="F14">
-        <v>5.668270308256072</v>
+        <v>4.607966659611927</v>
       </c>
       <c r="G14">
-        <v>-12.23260929781253</v>
+        <v>-10.80830583778002</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.112028578769095</v>
       </c>
       <c r="E15">
-        <v>-17.35697470071259</v>
+        <v>-13.90087989675652</v>
       </c>
       <c r="F15">
-        <v>6.340001718860219</v>
+        <v>4.766582449899976</v>
       </c>
       <c r="G15">
-        <v>-10.64910002186934</v>
+        <v>-10.17602004823666</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.285252399044623</v>
       </c>
       <c r="E16">
-        <v>-19.19481224406247</v>
+        <v>-14.3912952432036</v>
       </c>
       <c r="F16">
-        <v>6.071670322806181</v>
+        <v>5.210816007203684</v>
       </c>
       <c r="G16">
-        <v>-10.48224864042359</v>
+        <v>-9.764600640356889</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.549565347536416</v>
       </c>
       <c r="E17">
-        <v>-16.70901974229212</v>
+        <v>-15.55306058746391</v>
       </c>
       <c r="F17">
-        <v>6.620505145530993</v>
+        <v>5.083875329663883</v>
       </c>
       <c r="G17">
-        <v>-9.85990587165548</v>
+        <v>-9.35557528526717</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.895168447862641</v>
       </c>
       <c r="E18">
-        <v>-22.28851028744798</v>
+        <v>-17.15866716637468</v>
       </c>
       <c r="F18">
-        <v>6.46114548131523</v>
+        <v>5.390003473572857</v>
       </c>
       <c r="G18">
-        <v>-9.32429073283186</v>
+        <v>-8.4681727557694</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.288551241024464</v>
       </c>
       <c r="E19">
-        <v>-19.98269304522774</v>
+        <v>-17.46789451556479</v>
       </c>
       <c r="F19">
-        <v>6.496425649000461</v>
+        <v>5.695899674609047</v>
       </c>
       <c r="G19">
-        <v>-8.646204650926597</v>
+        <v>-7.6432074885404</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.723428174917215</v>
       </c>
       <c r="E20">
-        <v>-19.91805661737944</v>
+        <v>-18.50840270198541</v>
       </c>
       <c r="F20">
-        <v>7.719014755527057</v>
+        <v>5.837562097631402</v>
       </c>
       <c r="G20">
-        <v>-9.380885148705717</v>
+        <v>-6.96837831051255</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.181463748415466</v>
       </c>
       <c r="E21">
-        <v>-21.71772199544282</v>
+        <v>-18.90483502936294</v>
       </c>
       <c r="F21">
-        <v>6.862779416562571</v>
+        <v>6.229982930624805</v>
       </c>
       <c r="G21">
-        <v>-7.525049104463498</v>
+        <v>-6.595563982901574</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.6687480197166323</v>
       </c>
       <c r="E22">
-        <v>-21.24642388072392</v>
+        <v>-19.15332996935008</v>
       </c>
       <c r="F22">
-        <v>7.599420040115281</v>
+        <v>6.324373739439004</v>
       </c>
       <c r="G22">
-        <v>-8.272564022652533</v>
+        <v>-6.549301588747046</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.1863678879343632</v>
       </c>
       <c r="E23">
-        <v>-23.39863044888405</v>
+        <v>-19.12084355036728</v>
       </c>
       <c r="F23">
-        <v>7.888690907377286</v>
+        <v>6.526780344108646</v>
       </c>
       <c r="G23">
-        <v>-7.695777441627056</v>
+        <v>-6.024844772305845</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.2477625579534767</v>
       </c>
       <c r="E24">
-        <v>-23.58684983291395</v>
+        <v>-19.70990597220168</v>
       </c>
       <c r="F24">
-        <v>6.988959652826602</v>
+        <v>6.541001755679908</v>
       </c>
       <c r="G24">
-        <v>-7.667771984398184</v>
+        <v>-6.105960606751735</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.6198717643169425</v>
       </c>
       <c r="E25">
-        <v>-23.84256305418365</v>
+        <v>-20.68488479033915</v>
       </c>
       <c r="F25">
-        <v>7.914971691598502</v>
+        <v>6.224885157627978</v>
       </c>
       <c r="G25">
-        <v>-6.479881890069344</v>
+        <v>-5.750259709935505</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.9095281230251077</v>
       </c>
       <c r="E26">
-        <v>-23.48146624875776</v>
+        <v>-20.84604184937648</v>
       </c>
       <c r="F26">
-        <v>7.980187400486102</v>
+        <v>6.244245760566208</v>
       </c>
       <c r="G26">
-        <v>-7.330031704996519</v>
+        <v>-5.905139522058709</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.103662208310246</v>
       </c>
       <c r="E27">
-        <v>-22.44744953163784</v>
+        <v>-19.86328821963892</v>
       </c>
       <c r="F27">
-        <v>7.686488081088732</v>
+        <v>6.17195248058909</v>
       </c>
       <c r="G27">
-        <v>-7.402020376351876</v>
+        <v>-5.753173300899188</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.193794419886676</v>
       </c>
       <c r="E28">
-        <v>-21.85349047365146</v>
+        <v>-21.61149115617635</v>
       </c>
       <c r="F28">
-        <v>7.499757501149667</v>
+        <v>6.419488541363249</v>
       </c>
       <c r="G28">
-        <v>-7.050089394725214</v>
+        <v>-5.409199868786239</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.180675665456887</v>
       </c>
       <c r="E29">
-        <v>-23.52374594004451</v>
+        <v>-21.08881366415801</v>
       </c>
       <c r="F29">
-        <v>8.23935208286076</v>
+        <v>6.376615558063957</v>
       </c>
       <c r="G29">
-        <v>-7.95573711279798</v>
+        <v>-6.138772444772846</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.072360448569829</v>
       </c>
       <c r="E30">
-        <v>-23.23635202278902</v>
+        <v>-21.59901490935657</v>
       </c>
       <c r="F30">
-        <v>7.69706301935287</v>
+        <v>6.300308009652873</v>
       </c>
       <c r="G30">
-        <v>-7.043413720805738</v>
+        <v>-5.371432837531194</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.883999916496346</v>
       </c>
       <c r="E31">
-        <v>-21.24077136011083</v>
+        <v>-21.76151345565181</v>
       </c>
       <c r="F31">
-        <v>7.971441497447345</v>
+        <v>6.318368075768707</v>
       </c>
       <c r="G31">
-        <v>-6.585089675602027</v>
+        <v>-5.885261312741973</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.6370362755511136</v>
       </c>
       <c r="E32">
-        <v>-23.73807241046229</v>
+        <v>-20.22097523856713</v>
       </c>
       <c r="F32">
-        <v>7.418946947536964</v>
+        <v>6.301762622812189</v>
       </c>
       <c r="G32">
-        <v>-5.851005732961975</v>
+        <v>-5.754677089783669</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.3556071858795273</v>
       </c>
       <c r="E33">
-        <v>-23.32841210501517</v>
+        <v>-20.93365384227373</v>
       </c>
       <c r="F33">
-        <v>6.413752925466265</v>
+        <v>6.403953339091147</v>
       </c>
       <c r="G33">
-        <v>-7.524978614359539</v>
+        <v>-5.855365676429135</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.0653227227491255</v>
       </c>
       <c r="E34">
-        <v>-22.56002232459732</v>
+        <v>-20.96215317838471</v>
       </c>
       <c r="F34">
-        <v>8.063643759583346</v>
+        <v>6.637420407896159</v>
       </c>
       <c r="G34">
-        <v>-6.894418526990902</v>
+        <v>-6.287535282319072</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.210435746010538</v>
       </c>
       <c r="E35">
-        <v>-20.80580138485021</v>
+        <v>-19.49827078272239</v>
       </c>
       <c r="F35">
-        <v>8.306009151029231</v>
+        <v>6.900397237058502</v>
       </c>
       <c r="G35">
-        <v>-7.619842629822231</v>
+        <v>-6.493791937250795</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.4513835682231511</v>
       </c>
       <c r="E36">
-        <v>-22.40798156441799</v>
+        <v>-19.70075229444176</v>
       </c>
       <c r="F36">
-        <v>7.899595535867738</v>
+        <v>6.376416749887285</v>
       </c>
       <c r="G36">
-        <v>-8.851311272865935</v>
+        <v>-5.94821941855667</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6428304916791092</v>
       </c>
       <c r="E37">
-        <v>-21.74426932223112</v>
+        <v>-19.39900072563634</v>
       </c>
       <c r="F37">
-        <v>7.665377966195789</v>
+        <v>6.741362292864635</v>
       </c>
       <c r="G37">
-        <v>-8.792950688276187</v>
+        <v>-6.197647346047042</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.7769708184329011</v>
       </c>
       <c r="E38">
-        <v>-21.86711716000822</v>
+        <v>-19.52266674604444</v>
       </c>
       <c r="F38">
-        <v>7.923102946024382</v>
+        <v>6.823617519227821</v>
       </c>
       <c r="G38">
-        <v>-8.334113631760324</v>
+        <v>-6.191472935089059</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.8526111918060675</v>
       </c>
       <c r="E39">
-        <v>-21.85927174381562</v>
+        <v>-19.10130684429528</v>
       </c>
       <c r="F39">
-        <v>8.576433003142741</v>
+        <v>6.995174065082404</v>
       </c>
       <c r="G39">
-        <v>-8.456269065806218</v>
+        <v>-5.922561020715208</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.8757641976297752</v>
       </c>
       <c r="E40">
-        <v>-19.81673487389892</v>
+        <v>-18.75844263658539</v>
       </c>
       <c r="F40">
-        <v>8.101698958067956</v>
+        <v>7.33561484355014</v>
       </c>
       <c r="G40">
-        <v>-8.337711237806879</v>
+        <v>-6.267941644162767</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.856540457861556</v>
       </c>
       <c r="E41">
-        <v>-21.22312021198031</v>
+        <v>-18.11385177933802</v>
       </c>
       <c r="F41">
-        <v>8.343161429044789</v>
+        <v>7.295064602448298</v>
       </c>
       <c r="G41">
-        <v>-8.688840720844068</v>
+        <v>-6.513719750714763</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.8091654863785001</v>
       </c>
       <c r="E42">
-        <v>-19.27786816413639</v>
+        <v>-18.42708282424526</v>
       </c>
       <c r="F42">
-        <v>8.803521642946198</v>
+        <v>7.23571704824213</v>
       </c>
       <c r="G42">
-        <v>-8.451936535157266</v>
+        <v>-6.275893972187299</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.7478496041459312</v>
       </c>
       <c r="E43">
-        <v>-18.79915656720268</v>
+        <v>-16.53571454012967</v>
       </c>
       <c r="F43">
-        <v>8.035376550330216</v>
+        <v>7.445161462365958</v>
       </c>
       <c r="G43">
-        <v>-9.092584539625964</v>
+        <v>-6.618705622957202</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.6873396501628182</v>
       </c>
       <c r="E44">
-        <v>-19.05082040743067</v>
+        <v>-16.51427566327091</v>
       </c>
       <c r="F44">
-        <v>8.127988025963202</v>
+        <v>7.308916562157911</v>
       </c>
       <c r="G44">
-        <v>-8.802536037042461</v>
+        <v>-7.207204004218412</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.6392237672689692</v>
       </c>
       <c r="E45">
-        <v>-17.28216705832978</v>
+        <v>-16.05624290552352</v>
       </c>
       <c r="F45">
-        <v>7.765701542348837</v>
+        <v>6.987382441291672</v>
       </c>
       <c r="G45">
-        <v>-8.636644104233941</v>
+        <v>-6.755581740380089</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.612629838449978</v>
       </c>
       <c r="E46">
-        <v>-17.70633868414584</v>
+        <v>-15.52754325708417</v>
       </c>
       <c r="F46">
-        <v>7.922039322279188</v>
+        <v>7.683237567400147</v>
       </c>
       <c r="G46">
-        <v>-8.605364773287812</v>
+        <v>-6.967477603628617</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.6119277691375087</v>
       </c>
       <c r="E47">
-        <v>-18.06908016125637</v>
+        <v>-15.27380696440509</v>
       </c>
       <c r="F47">
-        <v>8.475681989409848</v>
+        <v>7.576633309599073</v>
       </c>
       <c r="G47">
-        <v>-9.455620323370926</v>
+        <v>-7.187999367006182</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.6378077810584404</v>
       </c>
       <c r="E48">
-        <v>-16.1432900616806</v>
+        <v>-14.41611068086945</v>
       </c>
       <c r="F48">
-        <v>7.771894417052167</v>
+        <v>7.335808681522394</v>
       </c>
       <c r="G48">
-        <v>-9.143910472914957</v>
+        <v>-6.838089101693043</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.6873663487509244</v>
       </c>
       <c r="E49">
-        <v>-17.24660310975527</v>
+        <v>-13.70223179908997</v>
       </c>
       <c r="F49">
-        <v>7.784369630138327</v>
+        <v>7.601910112528096</v>
       </c>
       <c r="G49">
-        <v>-8.355406864645444</v>
+        <v>-6.615491796365541</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.7564436130645397</v>
       </c>
       <c r="E50">
-        <v>-15.8398689019226</v>
+        <v>-13.8953395128492</v>
       </c>
       <c r="F50">
-        <v>8.436675825146825</v>
+        <v>7.207791126358953</v>
       </c>
       <c r="G50">
-        <v>-8.670314877225529</v>
+        <v>-7.154033579875799</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8399477108734997</v>
       </c>
       <c r="E51">
-        <v>-16.54755949882808</v>
+        <v>-12.5281106511383</v>
       </c>
       <c r="F51">
-        <v>7.47350322468534</v>
+        <v>7.24548184318633</v>
       </c>
       <c r="G51">
-        <v>-8.940928997072785</v>
+        <v>-7.039322684031463</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.9352273312786766</v>
       </c>
       <c r="E52">
-        <v>-15.10612521037647</v>
+        <v>-12.88009531091751</v>
       </c>
       <c r="F52">
-        <v>8.085552420652588</v>
+        <v>7.426958917056841</v>
       </c>
       <c r="G52">
-        <v>-9.89555297830254</v>
+        <v>-7.044251769819485</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.039373821823308</v>
       </c>
       <c r="E53">
-        <v>-13.90139904817213</v>
+        <v>-12.43286090261468</v>
       </c>
       <c r="F53">
-        <v>8.205037791567195</v>
+        <v>7.008697991300509</v>
       </c>
       <c r="G53">
-        <v>-8.786989053002381</v>
+        <v>-7.327204268604343</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.153896444394065</v>
       </c>
       <c r="E54">
-        <v>-14.39555643802288</v>
+        <v>-11.79843710669049</v>
       </c>
       <c r="F54">
-        <v>7.72799922837782</v>
+        <v>7.499500707254799</v>
       </c>
       <c r="G54">
-        <v>-9.854107407918617</v>
+        <v>-7.298553957461466</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.278434633653246</v>
       </c>
       <c r="E55">
-        <v>-14.27200255432055</v>
+        <v>-11.29866457512857</v>
       </c>
       <c r="F55">
-        <v>7.360414506855151</v>
+        <v>7.203407406063338</v>
       </c>
       <c r="G55">
-        <v>-8.875160424705754</v>
+        <v>-7.612276691997184</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.418397661240922</v>
       </c>
       <c r="E56">
-        <v>-12.2953979141855</v>
+        <v>-11.40741641366921</v>
       </c>
       <c r="F56">
-        <v>8.437219234163061</v>
+        <v>6.868967321061483</v>
       </c>
       <c r="G56">
-        <v>-8.642090117451003</v>
+        <v>-7.160489951249622</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.57506155901431</v>
       </c>
       <c r="E57">
-        <v>-13.80618252533911</v>
+        <v>-10.91390692478513</v>
       </c>
       <c r="F57">
-        <v>8.195688837059199</v>
+        <v>7.111150471678751</v>
       </c>
       <c r="G57">
-        <v>-8.50440466920487</v>
+        <v>-7.662575297289574</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.756358506898367</v>
       </c>
       <c r="E58">
-        <v>-13.69016672019135</v>
+        <v>-10.26108855590329</v>
       </c>
       <c r="F58">
-        <v>8.226053472576218</v>
+        <v>6.96667491295649</v>
       </c>
       <c r="G58">
-        <v>-9.908812950080804</v>
+        <v>-7.24375964998318</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.962675842827674</v>
       </c>
       <c r="E59">
-        <v>-12.84806989839176</v>
+        <v>-11.03471968901307</v>
       </c>
       <c r="F59">
-        <v>7.935043033768334</v>
+        <v>6.751128744543641</v>
       </c>
       <c r="G59">
-        <v>-10.81904905177245</v>
+        <v>-7.987840133662604</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.200810805836762</v>
       </c>
       <c r="E60">
-        <v>-12.08471796331092</v>
+        <v>-9.644320061320947</v>
       </c>
       <c r="F60">
-        <v>7.791854757990023</v>
+        <v>6.935334460638973</v>
       </c>
       <c r="G60">
-        <v>-9.378605968677675</v>
+        <v>-7.368266059533373</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.467251974342871</v>
       </c>
       <c r="E61">
-        <v>-11.9241132813798</v>
+        <v>-9.649328834178691</v>
       </c>
       <c r="F61">
-        <v>7.696625641364192</v>
+        <v>7.287531429287239</v>
       </c>
       <c r="G61">
-        <v>-9.683457393092793</v>
+        <v>-7.765394251521388</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.76622435192609</v>
       </c>
       <c r="E62">
-        <v>-12.08389978067993</v>
+        <v>-9.769340028620936</v>
       </c>
       <c r="F62">
-        <v>7.1403106609921</v>
+        <v>7.064978929381513</v>
       </c>
       <c r="G62">
-        <v>-9.585963052454554</v>
+        <v>-8.289652651373665</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.091942645547365</v>
       </c>
       <c r="E63">
-        <v>-11.38540024043629</v>
+        <v>-9.451104364067273</v>
       </c>
       <c r="F63">
-        <v>7.451907686494357</v>
+        <v>6.88566720790192</v>
       </c>
       <c r="G63">
-        <v>-10.42182426223457</v>
+        <v>-8.491567638050366</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.445442962608841</v>
       </c>
       <c r="E64">
-        <v>-10.89953681360123</v>
+        <v>-9.163739519291061</v>
       </c>
       <c r="F64">
-        <v>7.599189753977303</v>
+        <v>6.953126135716301</v>
       </c>
       <c r="G64">
-        <v>-9.669245804911068</v>
+        <v>-8.143257759171577</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.818036151538886</v>
       </c>
       <c r="E65">
-        <v>-13.66436697144151</v>
+        <v>-9.145810106001777</v>
       </c>
       <c r="F65">
-        <v>7.497350265477132</v>
+        <v>6.929537545554183</v>
       </c>
       <c r="G65">
-        <v>-10.62906908399402</v>
+        <v>-8.343909145466181</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.206906136037512</v>
       </c>
       <c r="E66">
-        <v>-14.70045614101251</v>
+        <v>-8.967446292445691</v>
       </c>
       <c r="F66">
-        <v>7.308272092318533</v>
+        <v>6.485004119250662</v>
       </c>
       <c r="G66">
-        <v>-10.21737946404907</v>
+        <v>-9.033338912619831</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.601868292085285</v>
       </c>
       <c r="E67">
-        <v>-12.06317525616904</v>
+        <v>-9.016761523716704</v>
       </c>
       <c r="F67">
-        <v>7.52554292166401</v>
+        <v>6.578878026805513</v>
       </c>
       <c r="G67">
-        <v>-11.02710059361056</v>
+        <v>-8.606333359531115</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.998911827851787</v>
       </c>
       <c r="E68">
-        <v>-11.09784434793914</v>
+        <v>-8.864484030491866</v>
       </c>
       <c r="F68">
-        <v>7.392886509044891</v>
+        <v>6.803607476245796</v>
       </c>
       <c r="G68">
-        <v>-11.09614565043944</v>
+        <v>-8.990478318667524</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.389889829858381</v>
       </c>
       <c r="E69">
-        <v>-11.42790420513459</v>
+        <v>-8.90546376663395</v>
       </c>
       <c r="F69">
-        <v>7.510731712501955</v>
+        <v>6.52953052388594</v>
       </c>
       <c r="G69">
-        <v>-10.03328541995131</v>
+        <v>-8.609817398187955</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.772750473768999</v>
       </c>
       <c r="E70">
-        <v>-11.03396795776328</v>
+        <v>-8.510813166914767</v>
       </c>
       <c r="F70">
-        <v>8.075855551835417</v>
+        <v>6.763716615596583</v>
       </c>
       <c r="G70">
-        <v>-11.51894398861958</v>
+        <v>-8.287310813475436</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.14247502627675</v>
       </c>
       <c r="E71">
-        <v>-11.01890426028812</v>
+        <v>-8.439872164275371</v>
       </c>
       <c r="F71">
-        <v>7.16094363626103</v>
+        <v>6.415477586398893</v>
       </c>
       <c r="G71">
-        <v>-9.446267330873264</v>
+        <v>-8.814209981481623</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.498383970426332</v>
       </c>
       <c r="E72">
-        <v>-11.35536006292381</v>
+        <v>-8.586567741479639</v>
       </c>
       <c r="F72">
-        <v>8.053688440136503</v>
+        <v>6.571493959776958</v>
       </c>
       <c r="G72">
-        <v>-9.476095087826733</v>
+        <v>-8.668825447436298</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.836824186474208</v>
       </c>
       <c r="E73">
-        <v>-8.968816852182885</v>
+        <v>-9.085351808746248</v>
       </c>
       <c r="F73">
-        <v>7.164918143059662</v>
+        <v>6.508803114733091</v>
       </c>
       <c r="G73">
-        <v>-9.480753961549574</v>
+        <v>-8.367897972141625</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.157680841840055</v>
       </c>
       <c r="E74">
-        <v>-11.63496255573392</v>
+        <v>-7.967959374280403</v>
       </c>
       <c r="F74">
-        <v>7.185667089764984</v>
+        <v>6.631300429524276</v>
       </c>
       <c r="G74">
-        <v>-10.5880934476365</v>
+        <v>-8.664673058164132</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.458829001098125</v>
       </c>
       <c r="E75">
-        <v>-11.20480615239878</v>
+        <v>-8.575441288340423</v>
       </c>
       <c r="F75">
-        <v>7.730666571414835</v>
+        <v>6.509439300898442</v>
       </c>
       <c r="G75">
-        <v>-10.53874384800298</v>
+        <v>-8.517852614593695</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.736398238177215</v>
       </c>
       <c r="E76">
-        <v>-9.576826224081158</v>
+        <v>-9.213972610264863</v>
       </c>
       <c r="F76">
-        <v>7.933429374067681</v>
+        <v>6.521699138459874</v>
       </c>
       <c r="G76">
-        <v>-11.70347533243635</v>
+        <v>-9.024834412114279</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.98435615102775</v>
       </c>
       <c r="E77">
-        <v>-12.01353192120336</v>
+        <v>-9.453791491794437</v>
       </c>
       <c r="F77">
-        <v>7.484263717247705</v>
+        <v>6.694372323573431</v>
       </c>
       <c r="G77">
-        <v>-10.99317657839364</v>
+        <v>-8.165912495360963</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.196247524678892</v>
       </c>
       <c r="E78">
-        <v>-11.86500893101617</v>
+        <v>-9.124059738293651</v>
       </c>
       <c r="F78">
-        <v>7.769835095688807</v>
+        <v>6.60618267313659</v>
       </c>
       <c r="G78">
-        <v>-9.600076737714112</v>
+        <v>-8.005037108284268</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.361805878632591</v>
       </c>
       <c r="E79">
-        <v>-12.33719583295858</v>
+        <v>-10.3018730911131</v>
       </c>
       <c r="F79">
-        <v>7.514447768670913</v>
+        <v>6.470182969679772</v>
       </c>
       <c r="G79">
-        <v>-10.27203148594714</v>
+        <v>-7.853749680718435</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.472883811093439</v>
       </c>
       <c r="E80">
-        <v>-13.86659098405874</v>
+        <v>-10.11848389185397</v>
       </c>
       <c r="F80">
-        <v>7.395303685126261</v>
+        <v>6.609053794554693</v>
       </c>
       <c r="G80">
-        <v>-9.838251050644491</v>
+        <v>-7.689729651781743</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.518022486699531</v>
       </c>
       <c r="E81">
-        <v>-13.22863695850845</v>
+        <v>-10.94406754542604</v>
       </c>
       <c r="F81">
-        <v>6.902131838399963</v>
+        <v>6.332826400417169</v>
       </c>
       <c r="G81">
-        <v>-9.469967670271389</v>
+        <v>-7.634554175593155</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.49207379100967</v>
       </c>
       <c r="E82">
-        <v>-15.99830976075348</v>
+        <v>-11.32582657719295</v>
       </c>
       <c r="F82">
-        <v>7.641863929099922</v>
+        <v>6.425842119342721</v>
       </c>
       <c r="G82">
-        <v>-8.014135553184298</v>
+        <v>-7.993791325958047</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.385705249199869</v>
       </c>
       <c r="E83">
-        <v>-16.37536735730069</v>
+        <v>-13.1323447539423</v>
       </c>
       <c r="F83">
-        <v>6.784621295373632</v>
+        <v>6.017995428574384</v>
       </c>
       <c r="G83">
-        <v>-9.236366076492347</v>
+        <v>-7.986735788700563</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.197896344152575</v>
       </c>
       <c r="E84">
-        <v>-17.31788882893463</v>
+        <v>-12.91458357775889</v>
       </c>
       <c r="F84">
-        <v>8.072783965505836</v>
+        <v>6.142386391248369</v>
       </c>
       <c r="G84">
-        <v>-9.137236104367775</v>
+        <v>-7.376309763618592</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.923216152695423</v>
       </c>
       <c r="E85">
-        <v>-16.921992265818</v>
+        <v>-14.22426139014165</v>
       </c>
       <c r="F85">
-        <v>7.414831618279856</v>
+        <v>6.129061273206936</v>
       </c>
       <c r="G85">
-        <v>-8.967061245057533</v>
+        <v>-7.607248397914701</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.566956685846524</v>
       </c>
       <c r="E86">
-        <v>-18.34819257513015</v>
+        <v>-14.94456113662931</v>
       </c>
       <c r="F86">
-        <v>6.563195375135712</v>
+        <v>5.881467226714581</v>
       </c>
       <c r="G86">
-        <v>-9.370563569964752</v>
+        <v>-7.517527549296501</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.129280799462704</v>
       </c>
       <c r="E87">
-        <v>-19.21314867206159</v>
+        <v>-16.24272209400832</v>
       </c>
       <c r="F87">
-        <v>6.824815338492269</v>
+        <v>6.123287552409423</v>
       </c>
       <c r="G87">
-        <v>-9.420890893447643</v>
+        <v>-6.867238065052822</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.621748152111226</v>
       </c>
       <c r="E88">
-        <v>-21.41434236779807</v>
+        <v>-18.38279297867729</v>
       </c>
       <c r="F88">
-        <v>6.481298003490537</v>
+        <v>5.996805790410773</v>
       </c>
       <c r="G88">
-        <v>-9.10175739074684</v>
+        <v>-7.258672223087619</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.050981072983162</v>
       </c>
       <c r="E89">
-        <v>-22.13058442682137</v>
+        <v>-19.80555442901248</v>
       </c>
       <c r="F89">
-        <v>6.91986387102429</v>
+        <v>5.451552828335665</v>
       </c>
       <c r="G89">
-        <v>-8.00504494051804</v>
+        <v>-6.959616651664774</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.435251620784754</v>
       </c>
       <c r="E90">
-        <v>-23.25956432088349</v>
+        <v>-21.15413537187491</v>
       </c>
       <c r="F90">
-        <v>7.365174305951637</v>
+        <v>5.685765427803197</v>
       </c>
       <c r="G90">
-        <v>-7.366018208440424</v>
+        <v>-7.233810102346447</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.784442738761973</v>
       </c>
       <c r="E91">
-        <v>-25.9566182231139</v>
+        <v>-22.739237546475</v>
       </c>
       <c r="F91">
-        <v>6.874750982267829</v>
+        <v>5.711817582621242</v>
       </c>
       <c r="G91">
-        <v>-8.728527954745877</v>
+        <v>-6.66187428477126</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.119118114401581</v>
       </c>
       <c r="E92">
-        <v>-26.02978119381208</v>
+        <v>-23.88806979066979</v>
       </c>
       <c r="F92">
-        <v>6.693293789214986</v>
+        <v>5.549409526363177</v>
       </c>
       <c r="G92">
-        <v>-7.766097847188693</v>
+        <v>-6.69193961948252</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.447218828809964</v>
       </c>
       <c r="E93">
-        <v>-29.26314342762892</v>
+        <v>-25.87998732095949</v>
       </c>
       <c r="F93">
-        <v>6.092682690345593</v>
+        <v>4.86309056579573</v>
       </c>
       <c r="G93">
-        <v>-7.573233006637086</v>
+        <v>-6.119967251483057</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.784416982741007</v>
       </c>
       <c r="E94">
-        <v>-29.74568843861545</v>
+        <v>-27.81316598348213</v>
       </c>
       <c r="F94">
-        <v>5.92965667200504</v>
+        <v>4.819969072275599</v>
       </c>
       <c r="G94">
-        <v>-7.640675066287019</v>
+        <v>-5.97814377306001</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.132421331358399</v>
       </c>
       <c r="E95">
-        <v>-34.68773580321398</v>
+        <v>-29.97625811852463</v>
       </c>
       <c r="F95">
-        <v>5.817210767279423</v>
+        <v>4.623354412486331</v>
       </c>
       <c r="G95">
-        <v>-6.669656914397368</v>
+        <v>-6.391056526845897</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.495378088511721</v>
       </c>
       <c r="E96">
-        <v>-35.86258583975316</v>
+        <v>-32.81404150989119</v>
       </c>
       <c r="F96">
-        <v>5.337309366345974</v>
+        <v>4.446897245076785</v>
       </c>
       <c r="G96">
-        <v>-6.012417628052146</v>
+        <v>-6.932457075683423</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.870703439272691</v>
       </c>
       <c r="E97">
-        <v>-37.83712841046543</v>
+        <v>-35.0897708126687</v>
       </c>
       <c r="F97">
-        <v>5.165789268657115</v>
+        <v>3.945208124714905</v>
       </c>
       <c r="G97">
-        <v>-6.690394058684581</v>
+        <v>-6.847477339242686</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.2513738142884913</v>
       </c>
       <c r="E98">
-        <v>-40.09584615965645</v>
+        <v>-38.27095625261172</v>
       </c>
       <c r="F98">
-        <v>5.359078861691545</v>
+        <v>3.655958795005373</v>
       </c>
       <c r="G98">
-        <v>-5.543345147366821</v>
+        <v>-6.517270363358677</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.3578690894154266</v>
       </c>
       <c r="E99">
-        <v>-42.96992861800201</v>
+        <v>-40.08438121979425</v>
       </c>
       <c r="F99">
-        <v>4.742276493567034</v>
+        <v>3.195464385584711</v>
       </c>
       <c r="G99">
-        <v>-7.973481038411482</v>
+        <v>-6.556770929022221</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.9711203046702095</v>
       </c>
       <c r="E100">
-        <v>-45.91713043832684</v>
+        <v>-42.68285034480721</v>
       </c>
       <c r="F100">
-        <v>4.767530102208779</v>
+        <v>3.02091411993641</v>
       </c>
       <c r="G100">
-        <v>-6.258242728006781</v>
+        <v>-6.605758940529871</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.559139909965747</v>
       </c>
       <c r="E101">
-        <v>-46.2817232093854</v>
+        <v>-44.80759795629323</v>
       </c>
       <c r="F101">
-        <v>3.638862948546397</v>
+        <v>2.798258902472737</v>
       </c>
       <c r="G101">
-        <v>-7.165124022898848</v>
+        <v>-5.995184103006207</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.15616165356517</v>
       </c>
       <c r="E102">
-        <v>-49.18391979349156</v>
+        <v>-46.7189649912407</v>
       </c>
       <c r="F102">
-        <v>3.645305990205371</v>
+        <v>2.28896371261835</v>
       </c>
       <c r="G102">
-        <v>-7.481789066588751</v>
+        <v>-6.578954425812911</v>
       </c>
     </row>
   </sheetData>
